--- a/data_input/maiz_terrain_constraints_irr.xlsx
+++ b/data_input/maiz_terrain_constraints_irr.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26924"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\pyaez_github_test_env\input\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\pyaez_github_test_env\input\maize_sugarcane_reduction_tables\M5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E85AE82-F717-4356-B6FB-39AB44A8621A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5B03592-4B5A-469B-A533-C1599F91AB3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{EE6CACD0-8D83-4948-BDC7-999A08C64FDC}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="15585" xr2:uid="{EE6CACD0-8D83-4948-BDC7-999A08C64FDC}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -137,9 +137,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -177,7 +177,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -283,7 +283,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -425,7 +425,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -435,6 +435,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5AC0B81-8C6D-4376-8A7F-61EB90836C63}">
   <dimension ref="A1:I7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="11.140625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -476,13 +479,13 @@
         <v>100</v>
       </c>
       <c r="D2">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="E2">
-        <v>50</v>
+        <v>55.55</v>
       </c>
       <c r="F2">
-        <v>25</v>
+        <v>16.66</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -514,7 +517,7 @@
         <v>100</v>
       </c>
       <c r="G3">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="H3">
         <v>0</v>
@@ -540,10 +543,10 @@
         <v>100</v>
       </c>
       <c r="F4">
-        <v>75</v>
+        <v>55.55</v>
       </c>
       <c r="G4">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="H4">
         <v>0</v>
@@ -569,7 +572,7 @@
         <v>100</v>
       </c>
       <c r="F5">
-        <v>50</v>
+        <v>77.77</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -598,7 +601,7 @@
         <v>100</v>
       </c>
       <c r="F6">
-        <v>25</v>
+        <v>16.66</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -624,10 +627,10 @@
         <v>100</v>
       </c>
       <c r="E7">
-        <v>100</v>
+        <v>55.55</v>
       </c>
       <c r="F7">
-        <v>25</v>
+        <v>16.66</v>
       </c>
       <c r="G7">
         <v>0</v>
